--- a/Lab8/Lab8/Лист Microsoft Excel.xlsx
+++ b/Lab8/Lab8/Лист Microsoft Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\tp-labs-Petuhova\Lab8\Lab8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E14A7-844A-42EF-8A97-8D83631339D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7949A563-530C-4AC8-B807-3371328D5297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6732" yWindow="1176" windowWidth="22692" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13620" yWindow="5052" windowWidth="22692" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,9 @@
       <c r="B2" s="7">
         <v>483</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="7">
+        <v>2</v>
+      </c>
       <c r="D2" s="7"/>
       <c r="E2" s="4"/>
     </row>
@@ -480,7 +482,9 @@
       <c r="B3" s="8">
         <v>3284</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="8">
+        <v>3255</v>
+      </c>
       <c r="D3" s="8"/>
       <c r="E3" s="4"/>
     </row>
@@ -491,7 +495,9 @@
       <c r="B4" s="8">
         <v>1465</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="8">
+        <v>1395</v>
+      </c>
       <c r="D4" s="8"/>
       <c r="E4" s="4"/>
     </row>
@@ -502,7 +508,9 @@
       <c r="B5" s="8">
         <v>1090</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7">
+        <v>1195</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="4"/>
     </row>
@@ -514,7 +522,9 @@
         <f>SUM(B2:B5)</f>
         <v>6322</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="7">
+        <v>5893</v>
+      </c>
       <c r="D6" s="7"/>
       <c r="E6" s="4"/>
     </row>

--- a/Lab8/Lab8/Лист Microsoft Excel.xlsx
+++ b/Lab8/Lab8/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\tp-labs-Petuhova\Lab8\Lab8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7949A563-530C-4AC8-B807-3371328D5297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB38A2E6-8313-4C82-B88B-067470571601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13620" yWindow="5052" windowWidth="22692" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -472,7 +472,9 @@
       <c r="C2" s="7">
         <v>2</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="7">
+        <v>2</v>
+      </c>
       <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -485,7 +487,9 @@
       <c r="C3" s="8">
         <v>3255</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -498,7 +502,9 @@
       <c r="C4" s="8">
         <v>1395</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8">
+        <v>1421</v>
+      </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -511,7 +517,9 @@
       <c r="C5" s="7">
         <v>1195</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="7">
+        <v>1113</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -525,7 +533,9 @@
       <c r="C6" s="7">
         <v>5893</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7">
+        <v>2570</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">

--- a/Lab8/Lab8/Лист Microsoft Excel.xlsx
+++ b/Lab8/Lab8/Лист Microsoft Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123\tp-labs-Petuhova\Lab8\Lab8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB38A2E6-8313-4C82-B88B-067470571601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFAAA16-2A4B-4163-AF83-736481B60BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13620" yWindow="5052" windowWidth="22692" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Этап</t>
   </si>
@@ -55,6 +55,18 @@
   </si>
   <si>
     <t>Итого</t>
+  </si>
+  <si>
+    <t>HashSet вместо List.Contains</t>
+  </si>
+  <si>
+    <t>StringBuilder вместо +=</t>
+  </si>
+  <si>
+    <t>List.Sort() вместо пузырьковой сортировку</t>
+  </si>
+  <si>
+    <t>Dictionary вместо двойного цикла</t>
   </si>
 </sst>
 </file>
@@ -473,9 +485,12 @@
         <v>2</v>
       </c>
       <c r="D2" s="7">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4"/>
+        <f>B2-C2</f>
+        <v>481</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -485,12 +500,15 @@
         <v>3284</v>
       </c>
       <c r="C3" s="8">
-        <v>3255</v>
-      </c>
-      <c r="D3" s="8">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="D3" s="7">
+        <f t="shared" ref="D3:D6" si="0">B3-C3</f>
+        <v>3284</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -500,12 +518,15 @@
         <v>1465</v>
       </c>
       <c r="C4" s="8">
-        <v>1395</v>
-      </c>
-      <c r="D4" s="8">
-        <v>1421</v>
-      </c>
-      <c r="E4" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="D4" s="7">
+        <f t="shared" si="0"/>
+        <v>1463</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -515,12 +536,15 @@
         <v>1090</v>
       </c>
       <c r="C5" s="7">
-        <v>1195</v>
+        <v>4</v>
       </c>
       <c r="D5" s="7">
-        <v>1113</v>
-      </c>
-      <c r="E5" s="4"/>
+        <f t="shared" si="0"/>
+        <v>1086</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -531,10 +555,11 @@
         <v>6322</v>
       </c>
       <c r="C6" s="7">
-        <v>5893</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7">
-        <v>2570</v>
+        <f t="shared" si="0"/>
+        <v>6282</v>
       </c>
       <c r="E6" s="4"/>
     </row>
